--- a/data/trans_bre/MCS12_SP_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/MCS12_SP_R2-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 16,88</t>
+          <t>2,56; 16,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 13,21</t>
+          <t>-1,86; 12,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 7,87</t>
+          <t>-6,99; 8,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 8,63</t>
+          <t>-3,06; 8,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 44,23</t>
+          <t>6,04; 45,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 28,19</t>
+          <t>-3,43; 26,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 16,82</t>
+          <t>-13,52; 18,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 22,37</t>
+          <t>-6,83; 22,87</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,74; 23,33</t>
+          <t>9,11; 23,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,56; 23,95</t>
+          <t>8,61; 22,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 13,72</t>
+          <t>-0,25; 13,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 18,83</t>
+          <t>6,88; 19,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,13; 67,68</t>
+          <t>21,19; 67,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,31; 53,37</t>
+          <t>16,23; 51,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 32,85</t>
+          <t>-0,43; 32,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,96; 55,44</t>
+          <t>16,95; 58,74</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 20,78</t>
+          <t>4,01; 20,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,82; 20,24</t>
+          <t>4,65; 19,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 19,35</t>
+          <t>0,56; 18,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,41; 47,51</t>
+          <t>7,39; 46,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 49,38</t>
+          <t>8,63; 50,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,45; 39,34</t>
+          <t>8,07; 39,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 40,39</t>
+          <t>1,2; 38,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,09; 452,19</t>
+          <t>15,92; 456,59</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 10,25</t>
+          <t>0,15; 9,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 14,3</t>
+          <t>4,62; 14,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 10,06</t>
+          <t>0,65; 9,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 36,37</t>
+          <t>4,4; 35,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 22,48</t>
+          <t>0,29; 21,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,61; 29,26</t>
+          <t>8,71; 29,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 21,07</t>
+          <t>1,22; 19,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 93,34</t>
+          <t>10,17; 85,85</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,65; 21,65</t>
+          <t>8,05; 22,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,64; 24,25</t>
+          <t>12,58; 24,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,35; 17,66</t>
+          <t>6,94; 18,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 21,27</t>
+          <t>2,16; 21,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,79; 55,94</t>
+          <t>16,65; 57,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,36; 56,93</t>
+          <t>25,13; 56,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,81; 37,14</t>
+          <t>12,81; 38,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 49,35</t>
+          <t>4,27; 49,07</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,65; 29,34</t>
+          <t>18,13; 29,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,49; 34,16</t>
+          <t>21,48; 34,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,29; 24,38</t>
+          <t>12,34; 25,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,73; 32,85</t>
+          <t>12,71; 32,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52,47; 118,09</t>
+          <t>53,21; 121,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>55,75; 122,43</t>
+          <t>56,4; 125,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,19; 88,64</t>
+          <t>33,12; 93,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36,69; 174,85</t>
+          <t>35,1; 175,47</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,43; 13,36</t>
+          <t>8,71; 13,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,72; 15,22</t>
+          <t>10,37; 15,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,26; 9,38</t>
+          <t>4,12; 9,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,53; 27,04</t>
+          <t>9,53; 25,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,81; 32,02</t>
+          <t>19,56; 32,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,48; 31,93</t>
+          <t>20,58; 32,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,55; 19,95</t>
+          <t>8,31; 19,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,81; 87,65</t>
+          <t>23,14; 80,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/MCS12_SP_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/MCS12_SP_R2-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>3,73</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 16,86</t>
+          <t>1,84; 17,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 12,75</t>
+          <t>-2,72; 13,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 8,26</t>
+          <t>-6,99; 8,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 8,75</t>
+          <t>-2,12; 9,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 45,17</t>
+          <t>4,18; 47,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 26,91</t>
+          <t>-4,96; 28,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 18,79</t>
+          <t>-13,55; 18,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 22,87</t>
+          <t>-4,73; 26,17</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,76</t>
+          <t>12,95</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,49%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,11; 23,43</t>
+          <t>8,86; 23,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,61; 22,98</t>
+          <t>8,06; 23,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 13,89</t>
+          <t>-0,27; 14,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,88; 19,06</t>
+          <t>6,47; 19,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,19; 67,35</t>
+          <t>19,54; 65,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,23; 51,67</t>
+          <t>15,54; 53,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 32,73</t>
+          <t>-0,67; 33,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,95; 58,74</t>
+          <t>17,18; 59,34</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25,66</t>
+          <t>9,38</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 20,78</t>
+          <t>2,79; 21,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 19,99</t>
+          <t>4,86; 20,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 18,51</t>
+          <t>-0,11; 17,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,39; 46,06</t>
+          <t>2,01; 17,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,63; 50,17</t>
+          <t>5,75; 49,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,07; 39,06</t>
+          <t>9,36; 40,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 38,68</t>
+          <t>-0,71; 37,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,92; 456,59</t>
+          <t>4,4; 42,78</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,42</t>
+          <t>6,16</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 9,91</t>
+          <t>0,46; 9,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 14,3</t>
+          <t>4,79; 14,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 9,34</t>
+          <t>0,41; 9,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 35,95</t>
+          <t>1,91; 10,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 21,38</t>
+          <t>1,13; 20,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,71; 29,05</t>
+          <t>8,69; 28,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 19,5</t>
+          <t>0,78; 20,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,17; 85,85</t>
+          <t>4,27; 26,25</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,34</t>
+          <t>9,63</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,05; 22,07</t>
+          <t>8,46; 22,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,58; 24,17</t>
+          <t>12,66; 23,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,94; 18,1</t>
+          <t>6,54; 17,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 21,64</t>
+          <t>3,99; 15,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,65; 57,58</t>
+          <t>17,87; 58,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,13; 56,23</t>
+          <t>25,91; 55,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,81; 38,69</t>
+          <t>12,49; 37,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,27; 49,07</t>
+          <t>8,14; 37,4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24,2</t>
+          <t>21,62</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>74,84%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,13; 29,58</t>
+          <t>18,24; 29,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,48; 34,07</t>
+          <t>21,5; 34,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,34; 25,45</t>
+          <t>11,73; 24,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,71; 32,81</t>
+          <t>10,6; 30,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>53,21; 121,39</t>
+          <t>54,56; 123,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>56,4; 125,2</t>
+          <t>56,81; 128,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,12; 93,66</t>
+          <t>30,5; 89,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>35,1; 175,47</t>
+          <t>26,58; 143,61</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,42</t>
+          <t>9,03</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,71; 13,61</t>
+          <t>8,28; 13,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,37; 15,27</t>
+          <t>10,41; 15,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,12; 9,1</t>
+          <t>4,26; 9,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,53; 25,77</t>
+          <t>6,82; 11,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,56; 32,59</t>
+          <t>18,48; 31,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,58; 32,09</t>
+          <t>20,76; 32,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,31; 19,38</t>
+          <t>8,78; 19,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,14; 80,67</t>
+          <t>15,84; 28,56</t>
         </is>
       </c>
     </row>
